--- a/artfynd/A 38006-2024 artfynd.xlsx
+++ b/artfynd/A 38006-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820163</v>
+        <v>119820164</v>
       </c>
       <c r="B3" t="n">
-        <v>91310</v>
+        <v>91352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670682</v>
+        <v>670670</v>
       </c>
       <c r="R3" t="n">
-        <v>7188694</v>
+        <v>7188549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820165</v>
+        <v>119820163</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670598</v>
+        <v>670682</v>
       </c>
       <c r="R4" t="n">
-        <v>7188303</v>
+        <v>7188694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820164</v>
+        <v>119820165</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670670</v>
+        <v>670598</v>
       </c>
       <c r="R5" t="n">
-        <v>7188549</v>
+        <v>7188303</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38006-2024 artfynd.xlsx
+++ b/artfynd/A 38006-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820164</v>
+        <v>119820163</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670670</v>
+        <v>670682</v>
       </c>
       <c r="R3" t="n">
-        <v>7188549</v>
+        <v>7188694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820163</v>
+        <v>119820164</v>
       </c>
       <c r="B4" t="n">
-        <v>91310</v>
+        <v>91352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1958</v>
+        <v>2014</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670682</v>
+        <v>670670</v>
       </c>
       <c r="R4" t="n">
-        <v>7188694</v>
+        <v>7188549</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38006-2024 artfynd.xlsx
+++ b/artfynd/A 38006-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119796464</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820163</v>
+        <v>119820165</v>
       </c>
       <c r="B3" t="n">
-        <v>91310</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670682</v>
+        <v>670598</v>
       </c>
       <c r="R3" t="n">
-        <v>7188694</v>
+        <v>7188303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>119820164</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820165</v>
+        <v>119820163</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670598</v>
+        <v>670682</v>
       </c>
       <c r="R5" t="n">
-        <v>7188303</v>
+        <v>7188694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38006-2024 artfynd.xlsx
+++ b/artfynd/A 38006-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820165</v>
+        <v>119820163</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670598</v>
+        <v>670682</v>
       </c>
       <c r="R3" t="n">
-        <v>7188303</v>
+        <v>7188694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820163</v>
+        <v>119820165</v>
       </c>
       <c r="B5" t="n">
-        <v>91328</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670682</v>
+        <v>670598</v>
       </c>
       <c r="R5" t="n">
-        <v>7188694</v>
+        <v>7188303</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38006-2024 artfynd.xlsx
+++ b/artfynd/A 38006-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820163</v>
+        <v>119820165</v>
       </c>
       <c r="B3" t="n">
-        <v>91328</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670682</v>
+        <v>670598</v>
       </c>
       <c r="R3" t="n">
-        <v>7188694</v>
+        <v>7188303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820165</v>
+        <v>119820163</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670598</v>
+        <v>670682</v>
       </c>
       <c r="R5" t="n">
-        <v>7188303</v>
+        <v>7188694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
